--- a/downloads/maharashtra.xlsx
+++ b/downloads/maharashtra.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="District table" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft roll by district and sex" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forms not collected by district" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State figures" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38 constituencies the CEO liste" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft roll by district and sex" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forms not collected by district" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State figures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -526,7 +527,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>No reasons, no split by sex of the names left off, nothing by constituency.</t>
+          <t>No reasons, no split by sex of the names left off. By constituency only the 38 seats the CEO chose to list.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -538,38 +539,42 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Draft roll by district and sex</t>
+          <t>38 constituencies the CEO liste</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Source table</t>
+          <t>Published table</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>constituency</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Annexure-1 of the press note of 31 August 2026.</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+          <t>The 38 constituencies the CEO listed with a high share of forms not collected</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>A selection the CEO made, which by its own title leaves out the seats a newspaper had called Muslim-heavy. It is 38 of 288 seats and cannot be ranked against the rest.</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>in this workbook only</t>
+          <t>data/maharashtra/top38.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Forms not collected by district</t>
+          <t>Draft roll by district and sex</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -587,7 +592,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Annexure-2 of the same note.</t>
+          <t>Annexure-1 of the press note of 31 August 2026.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr"/>
@@ -600,7 +605,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>State figures</t>
+          <t>Forms not collected by district</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -610,19 +615,50 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>district</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>The state figures with their source.</t>
+          <t>Annexure-2 of the same note.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>in this workbook only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>State figures</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Source table</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>The state figures with their source.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>in this workbook only</t>
         </is>
@@ -1827,6 +1863,972 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>constituency</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>total_electors</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>forms_not_collected</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>not_collected_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Colaba</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mumbai City</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>254910</v>
+      </c>
+      <c r="E2" t="n">
+        <v>119606</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>211</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Khadakwasala</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>597114</v>
+      </c>
+      <c r="E3" t="n">
+        <v>277851</v>
+      </c>
+      <c r="F3" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nalasopara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Palghar</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>662057</v>
+      </c>
+      <c r="E4" t="n">
+        <v>306851</v>
+      </c>
+      <c r="F4" t="n">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>210</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kothrud</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>448055</v>
+      </c>
+      <c r="E5" t="n">
+        <v>206861</v>
+      </c>
+      <c r="F5" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>144</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kalyan Rural</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>547750</v>
+      </c>
+      <c r="E6" t="n">
+        <v>252247</v>
+      </c>
+      <c r="F6" t="n">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>213</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hadapsar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>651473</v>
+      </c>
+      <c r="E7" t="n">
+        <v>298372</v>
+      </c>
+      <c r="F7" t="n">
+        <v>45.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>209</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Shivajinagar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>292851</v>
+      </c>
+      <c r="E8" t="n">
+        <v>129590</v>
+      </c>
+      <c r="F8" t="n">
+        <v>44.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>140</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ambarnath (SC)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>384026</v>
+      </c>
+      <c r="E9" t="n">
+        <v>169614</v>
+      </c>
+      <c r="F9" t="n">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>146</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ovala majiwada</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>567972</v>
+      </c>
+      <c r="E10" t="n">
+        <v>250750</v>
+      </c>
+      <c r="F10" t="n">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>150</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Airoli</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>497380</v>
+      </c>
+      <c r="E11" t="n">
+        <v>218863</v>
+      </c>
+      <c r="F11" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>138</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kalyan West</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>463143</v>
+      </c>
+      <c r="E12" t="n">
+        <v>197472</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>143</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dombivali</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>319686</v>
+      </c>
+      <c r="E13" t="n">
+        <v>132577</v>
+      </c>
+      <c r="F13" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>142</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kalyan East</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>346171</v>
+      </c>
+      <c r="E14" t="n">
+        <v>143549</v>
+      </c>
+      <c r="F14" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>188</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Panvel</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Raigad</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>684095</v>
+      </c>
+      <c r="E15" t="n">
+        <v>283356</v>
+      </c>
+      <c r="F15" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>145</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Meera Bhayandar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>514950</v>
+      </c>
+      <c r="E16" t="n">
+        <v>213045</v>
+      </c>
+      <c r="F16" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>206</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pimpri (SC)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>401975</v>
+      </c>
+      <c r="E17" t="n">
+        <v>165697</v>
+      </c>
+      <c r="F17" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>212</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Parvati</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>371234</v>
+      </c>
+      <c r="E18" t="n">
+        <v>151677</v>
+      </c>
+      <c r="F18" t="n">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>56</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nagpur West</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>399371</v>
+      </c>
+      <c r="E19" t="n">
+        <v>160515</v>
+      </c>
+      <c r="F19" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>182</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Worli</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mumbai City</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>268275</v>
+      </c>
+      <c r="E20" t="n">
+        <v>105575</v>
+      </c>
+      <c r="F20" t="n">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>208</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Vadgaon Sheri</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>518754</v>
+      </c>
+      <c r="E21" t="n">
+        <v>203814</v>
+      </c>
+      <c r="F21" t="n">
+        <v>39.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>205</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Chinchwad</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>687448</v>
+      </c>
+      <c r="E22" t="n">
+        <v>269733</v>
+      </c>
+      <c r="F22" t="n">
+        <v>39.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nashik West</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>493293</v>
+      </c>
+      <c r="E23" t="n">
+        <v>193236</v>
+      </c>
+      <c r="F23" t="n">
+        <v>39.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>151</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Belapur</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>422317</v>
+      </c>
+      <c r="E24" t="n">
+        <v>165170</v>
+      </c>
+      <c r="F24" t="n">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>185</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Malabar Hill</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mumbai City</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>261718</v>
+      </c>
+      <c r="E25" t="n">
+        <v>102049</v>
+      </c>
+      <c r="F25" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nashik East</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>416409</v>
+      </c>
+      <c r="E26" t="n">
+        <v>160590</v>
+      </c>
+      <c r="F26" t="n">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>53</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nagpur South</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>405701</v>
+      </c>
+      <c r="E27" t="n">
+        <v>153193</v>
+      </c>
+      <c r="F27" t="n">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>202</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Purandar</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>497770</v>
+      </c>
+      <c r="E28" t="n">
+        <v>187447</v>
+      </c>
+      <c r="F28" t="n">
+        <v>37.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>52</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nagpur South West</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>412341</v>
+      </c>
+      <c r="E29" t="n">
+        <v>153956</v>
+      </c>
+      <c r="F29" t="n">
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>54</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nagpur East</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>431679</v>
+      </c>
+      <c r="E30" t="n">
+        <v>157875</v>
+      </c>
+      <c r="F30" t="n">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>57</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nagpur North (SC)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>452837</v>
+      </c>
+      <c r="E31" t="n">
+        <v>165462</v>
+      </c>
+      <c r="F31" t="n">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>163</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Goregaon</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Mumbai Suburban</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>337369</v>
+      </c>
+      <c r="E32" t="n">
+        <v>122834</v>
+      </c>
+      <c r="F32" t="n">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>173</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Chembur</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Mumbai Suburban</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>262605</v>
+      </c>
+      <c r="E33" t="n">
+        <v>93297</v>
+      </c>
+      <c r="F33" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>159</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Dindoshi</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Mumbai Suburban</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>318102</v>
+      </c>
+      <c r="E34" t="n">
+        <v>112792</v>
+      </c>
+      <c r="F34" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>183</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Shivadi</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Mumbai City</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>275864</v>
+      </c>
+      <c r="E35" t="n">
+        <v>95266</v>
+      </c>
+      <c r="F35" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nashik (Central)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>350700</v>
+      </c>
+      <c r="E36" t="n">
+        <v>120790</v>
+      </c>
+      <c r="F36" t="n">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Boisar (ST)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Palghar</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>438287</v>
+      </c>
+      <c r="E37" t="n">
+        <v>150559</v>
+      </c>
+      <c r="F37" t="n">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>170</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ghatkopar East</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Mumbai Suburban</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>252056</v>
+      </c>
+      <c r="E38" t="n">
+        <v>85448</v>
+      </c>
+      <c r="F38" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>160</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kandivali East</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Mumbai Suburban</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>293280</v>
+      </c>
+      <c r="E39" t="n">
+        <v>98748</v>
+      </c>
+      <c r="F39" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2667,7 +3669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3171,7 +4173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3836,13 +4838,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4023,109 +5025,109 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Draft roll by district and sex</t>
+          <t>38 constituencies the CEO liste</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sr</t>
+          <t>ac</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serial number in the source table.</t>
+          <t>Assembly constituency number.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Draft roll by district and sex</t>
+          <t>38 constituencies the CEO liste</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>constituency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>District.</t>
+          <t>Constituency name, as the CEO's table prints it.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Draft roll by district and sex</t>
+          <t>38 constituencies the CEO liste</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>men</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Men on the roll.</t>
+          <t>District, as the CEO's table prints it.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Draft roll by district and sex</t>
+          <t>38 constituencies the CEO liste</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>total_electors</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Women on the roll.</t>
+          <t>Total electors, as the CEO's table prints them.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Draft roll by district and sex</t>
+          <t>38 constituencies the CEO liste</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>third_gender</t>
+          <t>forms_not_collected</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Third-gender electors on the roll.</t>
+          <t>Enumeration forms not collected, the names left off the draft.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Draft roll by district and sex</t>
+          <t>38 constituencies the CEO liste</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>not_collected_pct</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Total.</t>
+          <t>Forms not collected per 100 total electors, as printed.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Forms not collected by district</t>
+          <t>Draft roll by district and sex</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4142,7 +5144,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Forms not collected by district</t>
+          <t>Draft roll by district and sex</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4159,83 +5161,185 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Forms not collected by district</t>
+          <t>Draft roll by district and sex</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>uncollectable</t>
+          <t>men</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Enumeration forms not collected, the names left off.</t>
+          <t>Men on the roll.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>State figures</t>
+          <t>Draft roll by district and sex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>women</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What the row measures.</t>
+          <t>Women on the roll.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>State figures</t>
+          <t>Draft roll by district and sex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>third_gender</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The figure.</t>
+          <t>Third-gender electors on the roll.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>State figures</t>
+          <t>Draft roll by district and sex</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>total</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>The document the figure comes from.</t>
+          <t>Total.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Forms not collected by district</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>sr</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Serial number in the source table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Forms not collected by district</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>District.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Forms not collected by district</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>uncollectable</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Enumeration forms not collected, the names left off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>State figures</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>What the row measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>State figures</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>The figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>State figures</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The document the figure comes from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>State figures</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>quote</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>The words of the source.</t>
         </is>

--- a/downloads/maharashtra.xlsx
+++ b/downloads/maharashtra.xlsx
@@ -752,7 +752,7 @@
         <v>2859377</v>
       </c>
       <c r="E2" t="n">
-        <v>38.38</v>
+        <v>38.3782</v>
       </c>
       <c r="F2" t="n">
         <v>2350795</v>
@@ -764,7 +764,7 @@
         <v>694</v>
       </c>
       <c r="I2" t="n">
-        <v>48.78</v>
+        <v>48.782</v>
       </c>
     </row>
     <row r="3">
@@ -783,7 +783,7 @@
         <v>950720</v>
       </c>
       <c r="E3" t="n">
-        <v>37.2</v>
+        <v>37.2029</v>
       </c>
       <c r="F3" t="n">
         <v>815742</v>
@@ -795,7 +795,7 @@
         <v>60</v>
       </c>
       <c r="I3" t="n">
-        <v>49.16</v>
+        <v>49.1642</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +814,7 @@
         <v>2658202</v>
       </c>
       <c r="E4" t="n">
-        <v>33.95</v>
+        <v>33.9489</v>
       </c>
       <c r="F4" t="n">
         <v>2651474</v>
@@ -826,7 +826,7 @@
         <v>272</v>
       </c>
       <c r="I4" t="n">
-        <v>48.73</v>
+        <v>48.7269</v>
       </c>
     </row>
     <row r="5">
@@ -845,7 +845,7 @@
         <v>2866481</v>
       </c>
       <c r="E5" t="n">
-        <v>31.57</v>
+        <v>31.5686</v>
       </c>
       <c r="F5" t="n">
         <v>3151297</v>
@@ -857,7 +857,7 @@
         <v>383</v>
       </c>
       <c r="I5" t="n">
-        <v>49.28</v>
+        <v>49.2785</v>
       </c>
     </row>
     <row r="6">
@@ -876,7 +876,7 @@
         <v>1443267</v>
       </c>
       <c r="E6" t="n">
-        <v>31.11</v>
+        <v>31.1144</v>
       </c>
       <c r="F6" t="n">
         <v>1599760</v>
@@ -888,7 +888,7 @@
         <v>123</v>
       </c>
       <c r="I6" t="n">
-        <v>49.93</v>
+        <v>49.9305</v>
       </c>
     </row>
     <row r="7">
@@ -907,7 +907,7 @@
         <v>668709</v>
       </c>
       <c r="E7" t="n">
-        <v>28.14</v>
+        <v>28.1437</v>
       </c>
       <c r="F7" t="n">
         <v>863209</v>
@@ -919,7 +919,7 @@
         <v>96</v>
       </c>
       <c r="I7" t="n">
-        <v>49.44</v>
+        <v>49.4358</v>
       </c>
     </row>
     <row r="8">
@@ -938,7 +938,7 @@
         <v>584118</v>
       </c>
       <c r="E8" t="n">
-        <v>23.05</v>
+        <v>23.0536</v>
       </c>
       <c r="F8" t="n">
         <v>984312</v>
@@ -950,7 +950,7 @@
         <v>35</v>
       </c>
       <c r="I8" t="n">
-        <v>49.51</v>
+        <v>49.5109</v>
       </c>
     </row>
     <row r="9">
@@ -969,7 +969,7 @@
         <v>1027792</v>
       </c>
       <c r="E9" t="n">
-        <v>20.14</v>
+        <v>20.1352</v>
       </c>
       <c r="F9" t="n">
         <v>2109006</v>
@@ -981,7 +981,7 @@
         <v>64</v>
       </c>
       <c r="I9" t="n">
-        <v>48.26</v>
+        <v>48.2648</v>
       </c>
     </row>
     <row r="10">
@@ -1000,7 +1000,7 @@
         <v>607660</v>
       </c>
       <c r="E10" t="n">
-        <v>18.89</v>
+        <v>18.8939</v>
       </c>
       <c r="F10" t="n">
         <v>1352685</v>
@@ -1012,7 +1012,7 @@
         <v>78</v>
       </c>
       <c r="I10" t="n">
-        <v>48.14</v>
+        <v>48.1403</v>
       </c>
     </row>
     <row r="11">
@@ -1031,7 +1031,7 @@
         <v>276992</v>
       </c>
       <c r="E11" t="n">
-        <v>17.36</v>
+        <v>17.3593</v>
       </c>
       <c r="F11" t="n">
         <v>683405</v>
@@ -1043,7 +1043,7 @@
         <v>32</v>
       </c>
       <c r="I11" t="n">
-        <v>48.17</v>
+        <v>48.1715</v>
       </c>
     </row>
     <row r="12">
@@ -1062,7 +1062,7 @@
         <v>294857</v>
       </c>
       <c r="E12" t="n">
-        <v>16.07</v>
+        <v>16.0674</v>
       </c>
       <c r="F12" t="n">
         <v>791338</v>
@@ -1093,7 +1093,7 @@
         <v>622671</v>
       </c>
       <c r="E13" t="n">
-        <v>15.8</v>
+        <v>15.7994</v>
       </c>
       <c r="F13" t="n">
         <v>1709471</v>
@@ -1105,7 +1105,7 @@
         <v>244</v>
       </c>
       <c r="I13" t="n">
-        <v>48.48</v>
+        <v>48.4781</v>
       </c>
     </row>
     <row r="14">
@@ -1124,7 +1124,7 @@
         <v>178178</v>
       </c>
       <c r="E14" t="n">
-        <v>15.67</v>
+        <v>15.6676</v>
       </c>
       <c r="F14" t="n">
         <v>489686</v>
@@ -1136,7 +1136,7 @@
         <v>11</v>
       </c>
       <c r="I14" t="n">
-        <v>48.94</v>
+        <v>48.9401</v>
       </c>
     </row>
     <row r="15">
@@ -1155,7 +1155,7 @@
         <v>270104</v>
       </c>
       <c r="E15" t="n">
-        <v>15.03</v>
+        <v>15.0254</v>
       </c>
       <c r="F15" t="n">
         <v>780505</v>
@@ -1167,7 +1167,7 @@
         <v>24</v>
       </c>
       <c r="I15" t="n">
-        <v>48.9</v>
+        <v>48.9032</v>
       </c>
     </row>
     <row r="16">
@@ -1186,7 +1186,7 @@
         <v>382269</v>
       </c>
       <c r="E16" t="n">
-        <v>14.85</v>
+        <v>14.855</v>
       </c>
       <c r="F16" t="n">
         <v>1115046</v>
@@ -1198,7 +1198,7 @@
         <v>97</v>
       </c>
       <c r="I16" t="n">
-        <v>49.11</v>
+        <v>49.1051</v>
       </c>
     </row>
     <row r="17">
@@ -1217,7 +1217,7 @@
         <v>514743</v>
       </c>
       <c r="E17" t="n">
-        <v>14.49</v>
+        <v>14.4908</v>
       </c>
       <c r="F17" t="n">
         <v>1567375</v>
@@ -1229,7 +1229,7 @@
         <v>84</v>
       </c>
       <c r="I17" t="n">
-        <v>48.4</v>
+        <v>48.3957</v>
       </c>
     </row>
     <row r="18">
@@ -1248,7 +1248,7 @@
         <v>243183</v>
       </c>
       <c r="E18" t="n">
-        <v>14.45</v>
+        <v>14.4518</v>
       </c>
       <c r="F18" t="n">
         <v>749445</v>
@@ -1260,7 +1260,7 @@
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>47.94</v>
+        <v>47.9375</v>
       </c>
     </row>
     <row r="19">
@@ -1279,7 +1279,7 @@
         <v>160643</v>
       </c>
       <c r="E19" t="n">
-        <v>14.29</v>
+        <v>14.2946</v>
       </c>
       <c r="F19" t="n">
         <v>484974</v>
@@ -1291,7 +1291,7 @@
         <v>14</v>
       </c>
       <c r="I19" t="n">
-        <v>49.65</v>
+        <v>49.6463</v>
       </c>
     </row>
     <row r="20">
@@ -1310,7 +1310,7 @@
         <v>188729</v>
       </c>
       <c r="E20" t="n">
-        <v>13.99</v>
+        <v>13.9947</v>
       </c>
       <c r="F20" t="n">
         <v>583198</v>
@@ -1322,7 +1322,7 @@
         <v>14</v>
       </c>
       <c r="I20" t="n">
-        <v>49.72</v>
+        <v>49.7164</v>
       </c>
     </row>
     <row r="21">
@@ -1341,7 +1341,7 @@
         <v>388352</v>
       </c>
       <c r="E21" t="n">
-        <v>13.98</v>
+        <v>13.9842</v>
       </c>
       <c r="F21" t="n">
         <v>1239482</v>
@@ -1353,7 +1353,7 @@
         <v>79</v>
       </c>
       <c r="I21" t="n">
-        <v>48.11</v>
+        <v>48.1078</v>
       </c>
     </row>
     <row r="22">
@@ -1372,7 +1372,7 @@
         <v>353282</v>
       </c>
       <c r="E22" t="n">
-        <v>13.88</v>
+        <v>13.8777</v>
       </c>
       <c r="F22" t="n">
         <v>1124083</v>
@@ -1384,7 +1384,7 @@
         <v>61</v>
       </c>
       <c r="I22" t="n">
-        <v>48.73</v>
+        <v>48.7253</v>
       </c>
     </row>
     <row r="23">
@@ -1403,7 +1403,7 @@
         <v>449213</v>
       </c>
       <c r="E23" t="n">
-        <v>13.39</v>
+        <v>13.3884</v>
       </c>
       <c r="F23" t="n">
         <v>1475010</v>
@@ -1415,7 +1415,7 @@
         <v>174</v>
       </c>
       <c r="I23" t="n">
-        <v>49.24</v>
+        <v>49.2372</v>
       </c>
     </row>
     <row r="24">
@@ -1434,7 +1434,7 @@
         <v>133371</v>
       </c>
       <c r="E24" t="n">
-        <v>13.19</v>
+        <v>13.1948</v>
       </c>
       <c r="F24" t="n">
         <v>445598</v>
@@ -1446,7 +1446,7 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>49.21</v>
+        <v>49.2143</v>
       </c>
     </row>
     <row r="25">
@@ -1465,7 +1465,7 @@
         <v>134250</v>
       </c>
       <c r="E25" t="n">
-        <v>13.17</v>
+        <v>13.168</v>
       </c>
       <c r="F25" t="n">
         <v>461892</v>
@@ -1477,7 +1477,7 @@
         <v>17</v>
       </c>
       <c r="I25" t="n">
-        <v>47.82</v>
+        <v>47.8228</v>
       </c>
     </row>
     <row r="26">
@@ -1496,7 +1496,7 @@
         <v>341905</v>
       </c>
       <c r="E26" t="n">
-        <v>12.9</v>
+        <v>12.8955</v>
       </c>
       <c r="F26" t="n">
         <v>1183205</v>
@@ -1508,7 +1508,7 @@
         <v>83</v>
       </c>
       <c r="I26" t="n">
-        <v>48.76</v>
+        <v>48.763</v>
       </c>
     </row>
     <row r="27">
@@ -1527,7 +1527,7 @@
         <v>181545</v>
       </c>
       <c r="E27" t="n">
-        <v>12.84</v>
+        <v>12.8403</v>
       </c>
       <c r="F27" t="n">
         <v>652433</v>
@@ -1539,7 +1539,7 @@
         <v>26</v>
       </c>
       <c r="I27" t="n">
-        <v>47.05</v>
+        <v>47.0544</v>
       </c>
     </row>
     <row r="28">
@@ -1558,7 +1558,7 @@
         <v>82513</v>
       </c>
       <c r="E28" t="n">
-        <v>11.99</v>
+        <v>11.9929</v>
       </c>
       <c r="F28" t="n">
         <v>305758</v>
@@ -1570,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>49.5</v>
+        <v>49.5033</v>
       </c>
     </row>
     <row r="29">
@@ -1589,7 +1589,7 @@
         <v>264948</v>
       </c>
       <c r="E29" t="n">
-        <v>11.76</v>
+        <v>11.7586</v>
       </c>
       <c r="F29" t="n">
         <v>1022906</v>
@@ -1601,7 +1601,7 @@
         <v>45</v>
       </c>
       <c r="I29" t="n">
-        <v>48.55</v>
+        <v>48.5512</v>
       </c>
     </row>
     <row r="30">
@@ -1620,7 +1620,7 @@
         <v>180231</v>
       </c>
       <c r="E30" t="n">
-        <v>11.7</v>
+        <v>11.6957</v>
       </c>
       <c r="F30" t="n">
         <v>707316</v>
@@ -1632,7 +1632,7 @@
         <v>13</v>
       </c>
       <c r="I30" t="n">
-        <v>48.02</v>
+        <v>48.0202</v>
       </c>
     </row>
     <row r="31">
@@ -1651,7 +1651,7 @@
         <v>426915</v>
       </c>
       <c r="E31" t="n">
-        <v>11.2</v>
+        <v>11.2048</v>
       </c>
       <c r="F31" t="n">
         <v>1750199</v>
@@ -1663,7 +1663,7 @@
         <v>85</v>
       </c>
       <c r="I31" t="n">
-        <v>48.27</v>
+        <v>48.2652</v>
       </c>
     </row>
     <row r="32">
@@ -1682,7 +1682,7 @@
         <v>240407</v>
       </c>
       <c r="E32" t="n">
-        <v>10.96</v>
+        <v>10.9583</v>
       </c>
       <c r="F32" t="n">
         <v>1035959</v>
@@ -1694,7 +1694,7 @@
         <v>20</v>
       </c>
       <c r="I32" t="n">
-        <v>46.97</v>
+        <v>46.9659</v>
       </c>
     </row>
     <row r="33">
@@ -1713,7 +1713,7 @@
         <v>90603</v>
       </c>
       <c r="E33" t="n">
-        <v>10.93</v>
+        <v>10.9305</v>
       </c>
       <c r="F33" t="n">
         <v>372878</v>
@@ -1725,7 +1725,7 @@
         <v>12</v>
       </c>
       <c r="I33" t="n">
-        <v>49.49</v>
+        <v>49.4935</v>
       </c>
     </row>
     <row r="34">
@@ -1744,7 +1744,7 @@
         <v>214442</v>
       </c>
       <c r="E34" t="n">
-        <v>10.7</v>
+        <v>10.6983</v>
       </c>
       <c r="F34" t="n">
         <v>940200</v>
@@ -1756,7 +1756,7 @@
         <v>30</v>
       </c>
       <c r="I34" t="n">
-        <v>47.47</v>
+        <v>47.4734</v>
       </c>
     </row>
     <row r="35">
@@ -1775,7 +1775,7 @@
         <v>131569</v>
       </c>
       <c r="E35" t="n">
-        <v>9.9</v>
+        <v>9.8995</v>
       </c>
       <c r="F35" t="n">
         <v>587639</v>
@@ -1787,7 +1787,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>50.93</v>
+        <v>50.9262</v>
       </c>
     </row>
     <row r="36">
@@ -1806,7 +1806,7 @@
         <v>190937</v>
       </c>
       <c r="E36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.135899999999999</v>
       </c>
       <c r="F36" t="n">
         <v>991413</v>
@@ -1818,7 +1818,7 @@
         <v>27</v>
       </c>
       <c r="I36" t="n">
-        <v>47.79</v>
+        <v>47.7922</v>
       </c>
     </row>
     <row r="37">
@@ -1837,7 +1837,7 @@
         <v>85309</v>
       </c>
       <c r="E37" t="n">
-        <v>8.800000000000001</v>
+        <v>8.8003</v>
       </c>
       <c r="F37" t="n">
         <v>461211</v>
@@ -1849,7 +1849,7 @@
         <v>12</v>
       </c>
       <c r="I37" t="n">
-        <v>47.83</v>
+        <v>47.8299</v>
       </c>
     </row>
   </sheetData>
